--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_4/epoch_50/per_file_predictions_epoch_50.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_4/epoch_50/per_file_predictions_epoch_50.xlsx
@@ -919,7 +919,7 @@
     <t>0.0034,0.0002,0.9969,0.0003</t>
   </si>
   <si>
-    <t>0.0208,0.2412,0.8680,0.0029</t>
+    <t>0.0208,0.2411,0.8680,0.0029</t>
   </si>
   <si>
     <t>0.9453,0.0013,0.0393,0.0008</t>
@@ -1348,7 +1348,7 @@
     <t>0.8675,0.0091,0.1056,0.0007</t>
   </si>
   <si>
-    <t>0.9810,0.0061,0.0063,0.0005</t>
+    <t>0.9809,0.0061,0.0063,0.0005</t>
   </si>
   <si>
     <t>0.7961,0.0483,0.0900,0.0016</t>
@@ -1369,7 +1369,7 @@
     <t>0.0012,0.0004,0.9989,0.0000</t>
   </si>
   <si>
-    <t>0.0008,0.2492,0.9812,0.0025</t>
+    <t>0.0008,0.2493,0.9812,0.0025</t>
   </si>
   <si>
     <t>0.0696,0.0049,0.9443,0.0048</t>

--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_4/epoch_50/per_file_predictions_epoch_50.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_4/epoch_50/per_file_predictions_epoch_50.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="526">
   <si>
     <t>Filename</t>
   </si>
@@ -820,28 +820,34 @@
     <t>0,1,0,0</t>
   </si>
   <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9805,0.0025,0.0038,0.0015</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9804,0.0025,0.0038,0.0015</t>
   </si>
   <si>
     <t>0.0168,0.0008,0.0005,0.9965</t>
   </si>
   <si>
-    <t>0.9680,0.0013,0.0006,0.0121</t>
-  </si>
-  <si>
-    <t>0.7918,0.0005,0.0085,0.1007</t>
-  </si>
-  <si>
-    <t>0.9820,0.0024,0.0081,0.0009</t>
+    <t>0.9679,0.0013,0.0006,0.0121</t>
+  </si>
+  <si>
+    <t>0.7909,0.0005,0.0084,0.1016</t>
+  </si>
+  <si>
+    <t>0.9820,0.0024,0.0080,0.0009</t>
   </si>
   <si>
     <t>0.9823,0.0047,0.0060,0.0012</t>
   </si>
   <si>
-    <t>0.9689,0.0018,0.0213,0.0006</t>
+    <t>0.9690,0.0018,0.0212,0.0006</t>
   </si>
   <si>
     <t>0.9826,0.0016,0.0087,0.0006</t>
@@ -859,58 +865,58 @@
     <t>0.9807,0.0013,0.0107,0.0005</t>
   </si>
   <si>
-    <t>0.8848,0.0052,0.0840,0.0013</t>
-  </si>
-  <si>
-    <t>0.0915,0.0356,0.8708,0.0111</t>
-  </si>
-  <si>
-    <t>0.3290,0.0017,0.7537,0.0004</t>
-  </si>
-  <si>
-    <t>0.2495,0.0090,0.7648,0.0037</t>
-  </si>
-  <si>
-    <t>0.7356,0.0010,0.3058,0.0004</t>
-  </si>
-  <si>
-    <t>0.0061,0.9941,0.0315,0.0004</t>
+    <t>0.8848,0.0052,0.0838,0.0013</t>
+  </si>
+  <si>
+    <t>0.0916,0.0357,0.8706,0.0111</t>
+  </si>
+  <si>
+    <t>0.3289,0.0017,0.7537,0.0004</t>
+  </si>
+  <si>
+    <t>0.2496,0.0091,0.7645,0.0037</t>
+  </si>
+  <si>
+    <t>0.7359,0.0010,0.3052,0.0004</t>
+  </si>
+  <si>
+    <t>0.0061,0.9942,0.0314,0.0004</t>
   </si>
   <si>
     <t>0.0114,0.9848,0.0113,0.0022</t>
   </si>
   <si>
-    <t>0.6896,0.5027,0.0016,0.0001</t>
-  </si>
-  <si>
-    <t>0.0152,0.9786,0.0378,0.0066</t>
-  </si>
-  <si>
-    <t>0.0053,0.9970,0.0368,0.0000</t>
-  </si>
-  <si>
-    <t>0.8089,0.0006,0.2136,0.0007</t>
-  </si>
-  <si>
-    <t>0.3940,0.0106,0.6096,0.0071</t>
+    <t>0.6894,0.5028,0.0016,0.0001</t>
+  </si>
+  <si>
+    <t>0.0152,0.9786,0.0377,0.0066</t>
+  </si>
+  <si>
+    <t>0.0053,0.9970,0.0369,0.0000</t>
+  </si>
+  <si>
+    <t>0.8090,0.0006,0.2132,0.0007</t>
+  </si>
+  <si>
+    <t>0.3943,0.0106,0.6092,0.0072</t>
   </si>
   <si>
     <t>0.0832,0.0002,0.9617,0.0001</t>
   </si>
   <si>
-    <t>0.0985,0.0046,0.9246,0.0022</t>
-  </si>
-  <si>
-    <t>0.1254,0.0017,0.9188,0.0011</t>
-  </si>
-  <si>
-    <t>0.1905,0.0008,0.8791,0.0007</t>
-  </si>
-  <si>
-    <t>0.0171,0.0005,0.9879,0.0008</t>
-  </si>
-  <si>
-    <t>0.8625,0.0969,0.0401,0.0027</t>
+    <t>0.0987,0.0046,0.9244,0.0022</t>
+  </si>
+  <si>
+    <t>0.1255,0.0017,0.9186,0.0011</t>
+  </si>
+  <si>
+    <t>0.1906,0.0008,0.8790,0.0007</t>
+  </si>
+  <si>
+    <t>0.0171,0.0005,0.9878,0.0008</t>
+  </si>
+  <si>
+    <t>0.8625,0.0972,0.0400,0.0027</t>
   </si>
   <si>
     <t>0.9783,0.0141,0.0031,0.0011</t>
@@ -919,34 +925,34 @@
     <t>0.0034,0.0002,0.9969,0.0003</t>
   </si>
   <si>
-    <t>0.0208,0.2411,0.8680,0.0029</t>
-  </si>
-  <si>
-    <t>0.9453,0.0013,0.0393,0.0008</t>
+    <t>0.0207,0.2420,0.8678,0.0029</t>
+  </si>
+  <si>
+    <t>0.9454,0.0013,0.0392,0.0008</t>
   </si>
   <si>
     <t>0.9027,0.0072,0.0607,0.0017</t>
   </si>
   <si>
-    <t>0.5696,0.5817,0.0174,0.0013</t>
-  </si>
-  <si>
-    <t>0.0705,0.8976,0.2352,0.0056</t>
-  </si>
-  <si>
-    <t>0.0008,0.9210,0.9261,0.0002</t>
+    <t>0.5690,0.5822,0.0174,0.0013</t>
+  </si>
+  <si>
+    <t>0.0705,0.8977,0.2350,0.0056</t>
+  </si>
+  <si>
+    <t>0.0008,0.9212,0.9260,0.0002</t>
   </si>
   <si>
     <t>0.0019,0.0070,0.9933,0.0056</t>
   </si>
   <si>
-    <t>0.1012,0.0235,0.8534,0.0159</t>
-  </si>
-  <si>
-    <t>0.3438,0.0006,0.5961,0.0180</t>
-  </si>
-  <si>
-    <t>0.0033,0.8769,0.8240,0.0008</t>
+    <t>0.1012,0.0235,0.8532,0.0160</t>
+  </si>
+  <si>
+    <t>0.3437,0.0006,0.5959,0.0180</t>
+  </si>
+  <si>
+    <t>0.0033,0.8771,0.8237,0.0008</t>
   </si>
   <si>
     <t>0.0005,0.9941,0.0132,0.0018</t>
@@ -955,7 +961,7 @@
     <t>0.0092,0.0214,0.9801,0.0039</t>
   </si>
   <si>
-    <t>0.0057,0.1373,0.0044,0.9712</t>
+    <t>0.0057,0.1375,0.0044,0.9712</t>
   </si>
   <si>
     <t>0.0003,0.9993,0.0006,0.0000</t>
@@ -967,85 +973,85 @@
     <t>0.0006,0.9990,0.0311,0.0000</t>
   </si>
   <si>
-    <t>0.0022,0.0422,0.9875,0.0023</t>
-  </si>
-  <si>
-    <t>0.0023,0.1101,0.9840,0.0017</t>
+    <t>0.0022,0.0423,0.9875,0.0023</t>
+  </si>
+  <si>
+    <t>0.0023,0.1104,0.9840,0.0017</t>
   </si>
   <si>
     <t>0.0207,0.0027,0.9777,0.0023</t>
   </si>
   <si>
-    <t>0.1371,0.0001,0.9469,0.0000</t>
+    <t>0.1372,0.0001,0.9469,0.0000</t>
   </si>
   <si>
     <t>0.0459,0.0030,0.9636,0.0013</t>
   </si>
   <si>
-    <t>0.0472,0.0102,0.9389,0.0058</t>
-  </si>
-  <si>
-    <t>0.9665,0.0073,0.0167,0.0005</t>
-  </si>
-  <si>
-    <t>0.9318,0.0007,0.0640,0.0003</t>
+    <t>0.0472,0.0102,0.9387,0.0058</t>
+  </si>
+  <si>
+    <t>0.9665,0.0073,0.0166,0.0005</t>
+  </si>
+  <si>
+    <t>0.9318,0.0007,0.0639,0.0003</t>
   </si>
   <si>
     <t>0.9768,0.0087,0.0073,0.0016</t>
   </si>
   <si>
-    <t>0.2227,0.0009,0.8192,0.0007</t>
-  </si>
-  <si>
-    <t>0.9513,0.0006,0.0429,0.0004</t>
-  </si>
-  <si>
-    <t>0.9799,0.0013,0.0125,0.0005</t>
-  </si>
-  <si>
-    <t>0.9683,0.0013,0.0233,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.9972,0.7857,0.0000</t>
+    <t>0.2229,0.0009,0.8188,0.0007</t>
+  </si>
+  <si>
+    <t>0.9514,0.0006,0.0428,0.0004</t>
+  </si>
+  <si>
+    <t>0.9799,0.0013,0.0124,0.0005</t>
+  </si>
+  <si>
+    <t>0.9683,0.0013,0.0232,0.0004</t>
+  </si>
+  <si>
+    <t>0.0001,0.9972,0.7854,0.0000</t>
   </si>
   <si>
     <t>0.0021,0.0292,0.9946,0.0006</t>
   </si>
   <si>
-    <t>0.0081,0.0560,0.9790,0.0045</t>
-  </si>
-  <si>
-    <t>0.0005,0.9726,0.9199,0.0004</t>
+    <t>0.0081,0.0561,0.9789,0.0045</t>
+  </si>
+  <si>
+    <t>0.0005,0.9726,0.9198,0.0004</t>
   </si>
   <si>
     <t>0.0001,0.0003,0.9998,0.0001</t>
   </si>
   <si>
-    <t>0.0409,0.9807,0.0081,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.9987,0.0151,0.0001</t>
-  </si>
-  <si>
-    <t>0.9743,0.0017,0.0161,0.0003</t>
-  </si>
-  <si>
-    <t>0.4474,0.2136,0.2460,0.0075</t>
-  </si>
-  <si>
-    <t>0.0113,0.0108,0.9809,0.0030</t>
-  </si>
-  <si>
-    <t>0.0005,0.9672,0.9371,0.0003</t>
-  </si>
-  <si>
-    <t>0.0006,0.9387,0.9507,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.9977,0.3232,0.0001</t>
-  </si>
-  <si>
-    <t>0.0008,0.9626,0.9140,0.0005</t>
+    <t>0.0408,0.9807,0.0081,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.9987,0.0150,0.0001</t>
+  </si>
+  <si>
+    <t>0.9744,0.0017,0.0161,0.0003</t>
+  </si>
+  <si>
+    <t>0.4475,0.2143,0.2454,0.0075</t>
+  </si>
+  <si>
+    <t>0.0113,0.0109,0.9809,0.0030</t>
+  </si>
+  <si>
+    <t>0.0005,0.9673,0.9370,0.0003</t>
+  </si>
+  <si>
+    <t>0.0006,0.9388,0.9506,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.9977,0.3226,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.9626,0.9138,0.0005</t>
   </si>
   <si>
     <t>0.0064,0.0006,0.0020,0.9983</t>
@@ -1054,46 +1060,46 @@
     <t>0.0017,0.0003,0.0013,0.9996</t>
   </si>
   <si>
-    <t>0.0092,0.0001,0.0008,0.9983</t>
-  </si>
-  <si>
-    <t>0.0438,0.0002,0.0051,0.9836</t>
-  </si>
-  <si>
-    <t>0.0514,0.0007,0.0015,0.9858</t>
-  </si>
-  <si>
-    <t>0.0017,0.0005,0.0019,0.9995</t>
-  </si>
-  <si>
-    <t>0.0008,0.9953,0.5027,0.0000</t>
-  </si>
-  <si>
-    <t>0.0010,0.8946,0.9537,0.0005</t>
-  </si>
-  <si>
-    <t>0.0011,0.9553,0.7631,0.0009</t>
-  </si>
-  <si>
-    <t>0.0008,0.7764,0.9784,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.9906,0.9474,0.0000</t>
-  </si>
-  <si>
-    <t>0.0014,0.9823,0.5501,0.0003</t>
+    <t>0.0092,0.0001,0.0008,0.9984</t>
+  </si>
+  <si>
+    <t>0.0437,0.0002,0.0051,0.9837</t>
+  </si>
+  <si>
+    <t>0.0513,0.0007,0.0015,0.9858</t>
+  </si>
+  <si>
+    <t>0.0016,0.0005,0.0019,0.9995</t>
+  </si>
+  <si>
+    <t>0.0008,0.9953,0.5024,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.8947,0.9537,0.0005</t>
+  </si>
+  <si>
+    <t>0.0011,0.9554,0.7627,0.0009</t>
+  </si>
+  <si>
+    <t>0.0008,0.7769,0.9784,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.9906,0.9473,0.0000</t>
+  </si>
+  <si>
+    <t>0.0014,0.9824,0.5490,0.0003</t>
   </si>
   <si>
     <t>0.9921,0.0033,0.0019,0.0006</t>
   </si>
   <si>
-    <t>0.9563,0.0101,0.0211,0.0014</t>
+    <t>0.9562,0.0101,0.0211,0.0015</t>
   </si>
   <si>
     <t>0.9888,0.0089,0.0009,0.0009</t>
   </si>
   <si>
-    <t>0.9905,0.0040,0.0025,0.0004</t>
+    <t>0.9905,0.0041,0.0025,0.0004</t>
   </si>
   <si>
     <t>0.9760,0.0081,0.0077,0.0008</t>
@@ -1102,7 +1108,7 @@
     <t>0.9901,0.0040,0.0014,0.0025</t>
   </si>
   <si>
-    <t>0.9246,0.0024,0.0598,0.0011</t>
+    <t>0.9247,0.0024,0.0596,0.0011</t>
   </si>
   <si>
     <t>0.9885,0.0011,0.0015,0.0004</t>
@@ -1135,13 +1141,13 @@
     <t>0.0022,0.0002,0.9983,0.0000</t>
   </si>
   <si>
-    <t>0.2181,0.0043,0.8101,0.0022</t>
+    <t>0.2182,0.0043,0.8099,0.0022</t>
   </si>
   <si>
     <t>0.9748,0.0002,0.0262,0.0000</t>
   </si>
   <si>
-    <t>0.1568,0.0017,0.8929,0.0009</t>
+    <t>0.1570,0.0017,0.8928,0.0009</t>
   </si>
   <si>
     <t>0.0011,0.9989,0.0036,0.0001</t>
@@ -1153,7 +1159,7 @@
     <t>0.8844,0.1891,0.0015,0.0002</t>
   </si>
   <si>
-    <t>0.5621,0.6018,0.0117,0.0015</t>
+    <t>0.5618,0.6019,0.0117,0.0015</t>
   </si>
   <si>
     <t>0.0023,0.9980,0.0043,0.0002</t>
@@ -1162,22 +1168,22 @@
     <t>0.0002,0.9998,0.0021,0.0000</t>
   </si>
   <si>
-    <t>0.9340,0.0875,0.0099,0.0009</t>
-  </si>
-  <si>
-    <t>0.5005,0.0236,0.4532,0.0077</t>
-  </si>
-  <si>
-    <t>0.2686,0.0111,0.7122,0.0129</t>
-  </si>
-  <si>
-    <t>0.7437,0.0111,0.2318,0.0017</t>
-  </si>
-  <si>
-    <t>0.5129,0.0116,0.4724,0.0086</t>
-  </si>
-  <si>
-    <t>0.0039,0.6973,0.7828,0.0899</t>
+    <t>0.9339,0.0877,0.0099,0.0009</t>
+  </si>
+  <si>
+    <t>0.5007,0.0237,0.4528,0.0078</t>
+  </si>
+  <si>
+    <t>0.2684,0.0111,0.7123,0.0129</t>
+  </si>
+  <si>
+    <t>0.7437,0.0112,0.2317,0.0017</t>
+  </si>
+  <si>
+    <t>0.5131,0.0116,0.4721,0.0086</t>
+  </si>
+  <si>
+    <t>0.0039,0.6972,0.7828,0.0900</t>
   </si>
   <si>
     <t>0.0005,0.9994,0.0064,0.0000</t>
@@ -1186,19 +1192,19 @@
     <t>0.0001,0.9998,0.0016,0.0000</t>
   </si>
   <si>
-    <t>0.0003,0.9953,0.0030,0.0292</t>
+    <t>0.0003,0.9953,0.0030,0.0293</t>
   </si>
   <si>
     <t>0.0004,0.9977,0.0402,0.0004</t>
   </si>
   <si>
-    <t>0.0052,0.9923,0.2141,0.0003</t>
-  </si>
-  <si>
-    <t>0.5080,0.5144,0.0629,0.0042</t>
-  </si>
-  <si>
-    <t>0.1448,0.8771,0.0648,0.0084</t>
+    <t>0.0052,0.9923,0.2138,0.0003</t>
+  </si>
+  <si>
+    <t>0.5075,0.5151,0.0629,0.0042</t>
+  </si>
+  <si>
+    <t>0.1446,0.8772,0.0647,0.0084</t>
   </si>
   <si>
     <t>0.9936,0.0003,0.0023,0.0004</t>
@@ -1210,46 +1216,46 @@
     <t>0.9836,0.0035,0.0051,0.0018</t>
   </si>
   <si>
-    <t>0.9863,0.0014,0.0058,0.0006</t>
+    <t>0.9862,0.0014,0.0058,0.0006</t>
   </si>
   <si>
     <t>0.9955,0.0019,0.0006,0.0011</t>
   </si>
   <si>
-    <t>0.9576,0.0004,0.0176,0.0023</t>
-  </si>
-  <si>
-    <t>0.9826,0.0007,0.0088,0.0008</t>
-  </si>
-  <si>
-    <t>0.9816,0.0004,0.0108,0.0005</t>
-  </si>
-  <si>
-    <t>0.0028,0.9002,0.8625,0.0006</t>
-  </si>
-  <si>
-    <t>0.0005,0.6443,0.9880,0.0001</t>
-  </si>
-  <si>
-    <t>0.0008,0.0337,0.9966,0.0011</t>
-  </si>
-  <si>
-    <t>0.0372,0.0146,0.9615,0.0020</t>
+    <t>0.9576,0.0004,0.0175,0.0023</t>
+  </si>
+  <si>
+    <t>0.9826,0.0008,0.0088,0.0008</t>
+  </si>
+  <si>
+    <t>0.9817,0.0004,0.0107,0.0005</t>
+  </si>
+  <si>
+    <t>0.0028,0.9003,0.8623,0.0006</t>
+  </si>
+  <si>
+    <t>0.0005,0.6449,0.9880,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.0338,0.9966,0.0011</t>
+  </si>
+  <si>
+    <t>0.0373,0.0147,0.9615,0.0020</t>
   </si>
   <si>
     <t>0.9697,0.0008,0.0175,0.0002</t>
   </si>
   <si>
-    <t>0.6382,0.1090,0.1697,0.0075</t>
-  </si>
-  <si>
-    <t>0.2493,0.0010,0.8078,0.0025</t>
-  </si>
-  <si>
-    <t>0.7946,0.0124,0.1536,0.0032</t>
-  </si>
-  <si>
-    <t>0.0863,0.0001,0.0025,0.9717</t>
+    <t>0.6379,0.1093,0.1695,0.0075</t>
+  </si>
+  <si>
+    <t>0.2498,0.0010,0.8073,0.0025</t>
+  </si>
+  <si>
+    <t>0.7946,0.0124,0.1535,0.0032</t>
+  </si>
+  <si>
+    <t>0.0862,0.0001,0.0025,0.9718</t>
   </si>
   <si>
     <t>0.0001,0.0001,0.0017,1.0000</t>
@@ -1258,58 +1264,58 @@
     <t>0.0002,0.0002,0.0019,0.9999</t>
   </si>
   <si>
-    <t>0.0351,0.0001,0.0012,0.9922</t>
-  </si>
-  <si>
-    <t>0.0004,0.9817,0.8804,0.0002</t>
+    <t>0.0350,0.0001,0.0012,0.9922</t>
+  </si>
+  <si>
+    <t>0.0004,0.9817,0.8803,0.0002</t>
   </si>
   <si>
     <t>0.9657,0.0008,0.0236,0.0006</t>
   </si>
   <si>
-    <t>0.1505,0.8596,0.0576,0.0081</t>
+    <t>0.1501,0.8599,0.0576,0.0081</t>
   </si>
   <si>
     <t>0.9803,0.0005,0.0123,0.0004</t>
   </si>
   <si>
-    <t>0.1290,0.9068,0.0446,0.0027</t>
+    <t>0.1289,0.9069,0.0444,0.0027</t>
   </si>
   <si>
     <t>0.9897,0.0017,0.0020,0.0010</t>
   </si>
   <si>
-    <t>0.1242,0.0000,0.9433,0.0000</t>
-  </si>
-  <si>
-    <t>0.1262,0.0000,0.9201,0.0000</t>
+    <t>0.1241,0.0000,0.9434,0.0000</t>
+  </si>
+  <si>
+    <t>0.1261,0.0000,0.9201,0.0000</t>
   </si>
   <si>
     <t>0.0000,0.0000,1.0000,0.0000</t>
   </si>
   <si>
-    <t>0.8293,0.0001,0.1329,0.0026</t>
+    <t>0.8294,0.0001,0.1328,0.0026</t>
   </si>
   <si>
     <t>0.9426,0.0026,0.0252,0.0037</t>
   </si>
   <si>
-    <t>0.7964,0.1105,0.0454,0.0018</t>
-  </si>
-  <si>
-    <t>0.9894,0.0010,0.0043,0.0001</t>
-  </si>
-  <si>
-    <t>0.9437,0.0182,0.0168,0.0037</t>
-  </si>
-  <si>
-    <t>0.5704,0.4699,0.0426,0.0055</t>
-  </si>
-  <si>
-    <t>0.9482,0.0059,0.0305,0.0007</t>
-  </si>
-  <si>
-    <t>0.8921,0.0274,0.0502,0.0031</t>
+    <t>0.7962,0.1109,0.0454,0.0019</t>
+  </si>
+  <si>
+    <t>0.9894,0.0010,0.0042,0.0001</t>
+  </si>
+  <si>
+    <t>0.9436,0.0183,0.0168,0.0037</t>
+  </si>
+  <si>
+    <t>0.5700,0.4702,0.0425,0.0055</t>
+  </si>
+  <si>
+    <t>0.9481,0.0059,0.0305,0.0007</t>
+  </si>
+  <si>
+    <t>0.8920,0.0275,0.0501,0.0031</t>
   </si>
   <si>
     <t>0.9896,0.0012,0.0045,0.0003</t>
@@ -1318,64 +1324,64 @@
     <t>0.9952,0.0021,0.0005,0.0009</t>
   </si>
   <si>
-    <t>0.9767,0.0019,0.0119,0.0008</t>
-  </si>
-  <si>
-    <t>0.9538,0.0003,0.0354,0.0005</t>
+    <t>0.9767,0.0020,0.0119,0.0008</t>
+  </si>
+  <si>
+    <t>0.9538,0.0003,0.0353,0.0005</t>
   </si>
   <si>
     <t>0.9877,0.0017,0.0049,0.0003</t>
   </si>
   <si>
-    <t>0.9904,0.0023,0.0030,0.0004</t>
-  </si>
-  <si>
-    <t>0.9780,0.0018,0.0099,0.0008</t>
+    <t>0.9904,0.0023,0.0029,0.0004</t>
+  </si>
+  <si>
+    <t>0.9780,0.0019,0.0099,0.0008</t>
   </si>
   <si>
     <t>0.9692,0.0005,0.0218,0.0005</t>
   </si>
   <si>
-    <t>0.8870,0.1316,0.0065,0.0021</t>
-  </si>
-  <si>
-    <t>0.7799,0.2879,0.0138,0.0028</t>
-  </si>
-  <si>
-    <t>0.8319,0.1897,0.0132,0.0022</t>
-  </si>
-  <si>
-    <t>0.8675,0.0091,0.1056,0.0007</t>
+    <t>0.8868,0.1317,0.0065,0.0021</t>
+  </si>
+  <si>
+    <t>0.7796,0.2882,0.0138,0.0029</t>
+  </si>
+  <si>
+    <t>0.8316,0.1902,0.0132,0.0022</t>
+  </si>
+  <si>
+    <t>0.8678,0.0091,0.1053,0.0007</t>
   </si>
   <si>
     <t>0.9809,0.0061,0.0063,0.0005</t>
   </si>
   <si>
-    <t>0.7961,0.0483,0.0900,0.0016</t>
-  </si>
-  <si>
-    <t>0.9759,0.0018,0.0138,0.0004</t>
-  </si>
-  <si>
-    <t>0.9696,0.0132,0.0096,0.0011</t>
+    <t>0.7959,0.0485,0.0899,0.0016</t>
+  </si>
+  <si>
+    <t>0.9759,0.0019,0.0138,0.0004</t>
+  </si>
+  <si>
+    <t>0.9696,0.0133,0.0096,0.0011</t>
   </si>
   <si>
     <t>0.0082,0.0036,0.9904,0.0005</t>
   </si>
   <si>
-    <t>0.8060,0.0308,0.1189,0.0016</t>
+    <t>0.8060,0.0309,0.1187,0.0016</t>
   </si>
   <si>
     <t>0.0012,0.0004,0.9989,0.0000</t>
   </si>
   <si>
-    <t>0.0008,0.2493,0.9812,0.0025</t>
+    <t>0.0008,0.2496,0.9812,0.0025</t>
   </si>
   <si>
     <t>0.0696,0.0049,0.9443,0.0048</t>
   </si>
   <si>
-    <t>0.0023,0.6482,0.9070,0.0008</t>
+    <t>0.0023,0.6492,0.9067,0.0008</t>
   </si>
   <si>
     <t>0.0037,0.0023,0.9956,0.0002</t>
@@ -1387,70 +1393,70 @@
     <t>0.0239,0.0008,0.9854,0.0004</t>
   </si>
   <si>
-    <t>0.3285,0.0095,0.7097,0.0041</t>
-  </si>
-  <si>
-    <t>0.3634,0.0028,0.7024,0.0014</t>
-  </si>
-  <si>
-    <t>0.6600,0.0483,0.2503,0.0080</t>
-  </si>
-  <si>
-    <t>0.0956,0.0175,0.8825,0.0116</t>
-  </si>
-  <si>
-    <t>0.0373,0.0144,0.9493,0.0016</t>
-  </si>
-  <si>
-    <t>0.1096,0.0079,0.8870,0.0071</t>
-  </si>
-  <si>
-    <t>0.4022,0.0063,0.6252,0.0029</t>
-  </si>
-  <si>
-    <t>0.6421,0.0311,0.3053,0.0066</t>
-  </si>
-  <si>
-    <t>0.8732,0.1902,0.0016,0.0001</t>
-  </si>
-  <si>
-    <t>0.0876,0.9525,0.0303,0.0008</t>
-  </si>
-  <si>
-    <t>0.5155,0.5564,0.0391,0.0026</t>
-  </si>
-  <si>
-    <t>0.9141,0.0271,0.0321,0.0015</t>
-  </si>
-  <si>
-    <t>0.7235,0.2847,0.0299,0.0024</t>
-  </si>
-  <si>
-    <t>0.5328,0.4729,0.0329,0.0015</t>
+    <t>0.3287,0.0096,0.7093,0.0041</t>
+  </si>
+  <si>
+    <t>0.3635,0.0028,0.7021,0.0014</t>
+  </si>
+  <si>
+    <t>0.6601,0.0484,0.2501,0.0080</t>
+  </si>
+  <si>
+    <t>0.0957,0.0175,0.8823,0.0116</t>
+  </si>
+  <si>
+    <t>0.0374,0.0145,0.9491,0.0016</t>
+  </si>
+  <si>
+    <t>0.1095,0.0079,0.8870,0.0071</t>
+  </si>
+  <si>
+    <t>0.4026,0.0063,0.6245,0.0029</t>
+  </si>
+  <si>
+    <t>0.6421,0.0312,0.3052,0.0067</t>
+  </si>
+  <si>
+    <t>0.8729,0.1904,0.0016,0.0001</t>
+  </si>
+  <si>
+    <t>0.0874,0.9526,0.0303,0.0008</t>
+  </si>
+  <si>
+    <t>0.5153,0.5569,0.0390,0.0026</t>
+  </si>
+  <si>
+    <t>0.9140,0.0272,0.0320,0.0016</t>
+  </si>
+  <si>
+    <t>0.7231,0.2855,0.0298,0.0024</t>
+  </si>
+  <si>
+    <t>0.5322,0.4737,0.0328,0.0015</t>
   </si>
   <si>
     <t>0.9466,0.0067,0.0182,0.0010</t>
   </si>
   <si>
-    <t>0.6932,0.0339,0.2075,0.0147</t>
-  </si>
-  <si>
-    <t>0.2193,0.0049,0.7713,0.0115</t>
-  </si>
-  <si>
-    <t>0.5524,0.0048,0.4318,0.0035</t>
-  </si>
-  <si>
-    <t>0.0329,0.0017,0.9745,0.0023</t>
-  </si>
-  <si>
-    <t>0.2566,0.0043,0.7465,0.0014</t>
-  </si>
-  <si>
-    <t>0.1631,0.0197,0.7294,0.0016</t>
-  </si>
-  <si>
-    <t>0.0127,0.0121,0.9831,0.0026</t>
+    <t>0.6931,0.0340,0.2075,0.0147</t>
+  </si>
+  <si>
+    <t>0.2193,0.0049,0.7711,0.0115</t>
+  </si>
+  <si>
+    <t>0.5528,0.0048,0.4313,0.0035</t>
+  </si>
+  <si>
+    <t>0.0329,0.0017,0.9744,0.0023</t>
+  </si>
+  <si>
+    <t>0.2567,0.0044,0.7463,0.0014</t>
+  </si>
+  <si>
+    <t>0.1629,0.0198,0.7295,0.0016</t>
+  </si>
+  <si>
+    <t>0.0128,0.0121,0.9831,0.0026</t>
   </si>
   <si>
     <t>0.0276,0.0020,0.9791,0.0003</t>
@@ -1459,16 +1465,16 @@
     <t>0.9619,0.0009,0.0273,0.0006</t>
   </si>
   <si>
-    <t>0.9641,0.0121,0.0143,0.0024</t>
-  </si>
-  <si>
-    <t>0.9539,0.0156,0.0189,0.0035</t>
+    <t>0.9640,0.0121,0.0143,0.0025</t>
+  </si>
+  <si>
+    <t>0.9539,0.0157,0.0189,0.0035</t>
   </si>
   <si>
     <t>0.9893,0.0076,0.0018,0.0016</t>
   </si>
   <si>
-    <t>0.9645,0.0138,0.0118,0.0034</t>
+    <t>0.9645,0.0139,0.0118,0.0034</t>
   </si>
   <si>
     <t>0.9675,0.0117,0.0105,0.0030</t>
@@ -1477,16 +1483,16 @@
     <t>0.9686,0.0063,0.0131,0.0017</t>
   </si>
   <si>
-    <t>0.9566,0.0015,0.0301,0.0008</t>
+    <t>0.9565,0.0015,0.0301,0.0008</t>
   </si>
   <si>
     <t>0.0293,0.0010,0.9806,0.0008</t>
   </si>
   <si>
-    <t>0.1513,0.0243,0.8394,0.0029</t>
-  </si>
-  <si>
-    <t>0.5894,0.0104,0.3867,0.0085</t>
+    <t>0.1514,0.0244,0.8391,0.0029</t>
+  </si>
+  <si>
+    <t>0.5893,0.0104,0.3864,0.0085</t>
   </si>
   <si>
     <t>0.0011,0.0005,0.9989,0.0001</t>
@@ -1495,13 +1501,13 @@
     <t>0.0005,0.0057,0.9983,0.0005</t>
   </si>
   <si>
-    <t>0.0219,0.0479,0.9524,0.0024</t>
+    <t>0.0219,0.0481,0.9522,0.0024</t>
   </si>
   <si>
     <t>0.0001,0.0002,0.9998,0.0000</t>
   </si>
   <si>
-    <t>0.0653,0.0107,0.9315,0.0028</t>
+    <t>0.0653,0.0107,0.9314,0.0028</t>
   </si>
   <si>
     <t>0.0000,0.0002,0.9999,0.0000</t>
@@ -1510,19 +1516,19 @@
     <t>0.0074,0.0183,0.9853,0.0029</t>
   </si>
   <si>
-    <t>0.1864,0.0404,0.7462,0.0125</t>
-  </si>
-  <si>
-    <t>0.7236,0.0024,0.2315,0.0044</t>
-  </si>
-  <si>
-    <t>0.8265,0.0006,0.1384,0.0019</t>
-  </si>
-  <si>
-    <t>0.9510,0.0038,0.0251,0.0004</t>
-  </si>
-  <si>
-    <t>0.9776,0.0061,0.0070,0.0009</t>
+    <t>0.1865,0.0405,0.7459,0.0125</t>
+  </si>
+  <si>
+    <t>0.7237,0.0024,0.2313,0.0044</t>
+  </si>
+  <si>
+    <t>0.8266,0.0006,0.1382,0.0019</t>
+  </si>
+  <si>
+    <t>0.9511,0.0038,0.0250,0.0004</t>
+  </si>
+  <si>
+    <t>0.9776,0.0062,0.0070,0.0009</t>
   </si>
   <si>
     <t>0.9894,0.0092,0.0013,0.0008</t>
@@ -1531,10 +1537,10 @@
     <t>0.9720,0.0055,0.0127,0.0012</t>
   </si>
   <si>
-    <t>0.9246,0.0230,0.0343,0.0025</t>
-  </si>
-  <si>
-    <t>0.9703,0.0020,0.0151,0.0009</t>
+    <t>0.9246,0.0231,0.0342,0.0025</t>
+  </si>
+  <si>
+    <t>0.9703,0.0020,0.0150,0.0009</t>
   </si>
   <si>
     <t>0.9693,0.0165,0.0083,0.0020</t>
@@ -1546,7 +1552,7 @@
     <t>0.9649,0.0043,0.0169,0.0017</t>
   </si>
   <si>
-    <t>0.0178,0.0574,0.9458,0.0032</t>
+    <t>0.0178,0.0576,0.9457,0.0032</t>
   </si>
   <si>
     <t>0.0047,0.0175,0.9919,0.0008</t>
@@ -1555,28 +1561,28 @@
     <t>0.0068,0.0077,0.9908,0.0005</t>
   </si>
   <si>
-    <t>0.0522,0.0213,0.9245,0.0027</t>
-  </si>
-  <si>
-    <t>0.0368,0.0009,0.9782,0.0005</t>
-  </si>
-  <si>
-    <t>0.8783,0.0073,0.0500,0.0090</t>
-  </si>
-  <si>
-    <t>0.4339,0.0057,0.5955,0.0034</t>
+    <t>0.0522,0.0214,0.9244,0.0027</t>
+  </si>
+  <si>
+    <t>0.0369,0.0009,0.9782,0.0005</t>
+  </si>
+  <si>
+    <t>0.8783,0.0073,0.0499,0.0090</t>
+  </si>
+  <si>
+    <t>0.4343,0.0057,0.5948,0.0034</t>
   </si>
   <si>
     <t>0.0011,0.0017,0.9963,0.0033</t>
   </si>
   <si>
-    <t>0.9619,0.0004,0.0016,0.0156</t>
+    <t>0.9618,0.0004,0.0016,0.0156</t>
   </si>
   <si>
     <t>0.0009,0.0015,0.0006,0.9997</t>
   </si>
   <si>
-    <t>0.1588,0.0003,0.0011,0.9482</t>
+    <t>0.1583,0.0003,0.0011,0.9484</t>
   </si>
   <si>
     <t>0.0005,0.0002,0.0187,0.9996</t>
@@ -1585,7 +1591,7 @@
     <t>0.0002,0.0003,0.0019,0.9999</t>
   </si>
   <si>
-    <t>0.7475,0.0066,0.0085,0.1441</t>
+    <t>0.7476,0.0066,0.0084,0.1440</t>
   </si>
 </sst>
 </file>
@@ -1971,7 +1977,7 @@
         <v>264</v>
       </c>
       <c r="D2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1985,7 +1991,7 @@
         <v>265</v>
       </c>
       <c r="D3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1999,7 +2005,7 @@
         <v>264</v>
       </c>
       <c r="D4" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2013,7 +2019,7 @@
         <v>264</v>
       </c>
       <c r="D5" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2027,7 +2033,7 @@
         <v>264</v>
       </c>
       <c r="D6" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2041,7 +2047,7 @@
         <v>264</v>
       </c>
       <c r="D7" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2055,7 +2061,7 @@
         <v>264</v>
       </c>
       <c r="D8" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2069,7 +2075,7 @@
         <v>264</v>
       </c>
       <c r="D9" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2083,7 +2089,7 @@
         <v>264</v>
       </c>
       <c r="D10" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2097,7 +2103,7 @@
         <v>264</v>
       </c>
       <c r="D11" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2111,7 +2117,7 @@
         <v>264</v>
       </c>
       <c r="D12" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2125,7 +2131,7 @@
         <v>264</v>
       </c>
       <c r="D13" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2139,7 +2145,7 @@
         <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2153,7 +2159,7 @@
         <v>266</v>
       </c>
       <c r="D15" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2167,7 +2173,7 @@
         <v>266</v>
       </c>
       <c r="D16" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2181,7 +2187,7 @@
         <v>266</v>
       </c>
       <c r="D17" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2195,7 +2201,7 @@
         <v>264</v>
       </c>
       <c r="D18" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2209,7 +2215,7 @@
         <v>267</v>
       </c>
       <c r="D19" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2223,7 +2229,7 @@
         <v>267</v>
       </c>
       <c r="D20" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2234,10 +2240,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D21" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2251,7 +2257,7 @@
         <v>267</v>
       </c>
       <c r="D22" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2265,7 +2271,7 @@
         <v>267</v>
       </c>
       <c r="D23" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2279,7 +2285,7 @@
         <v>264</v>
       </c>
       <c r="D24" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2293,7 +2299,7 @@
         <v>266</v>
       </c>
       <c r="D25" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2307,7 +2313,7 @@
         <v>266</v>
       </c>
       <c r="D26" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2321,7 +2327,7 @@
         <v>266</v>
       </c>
       <c r="D27" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2335,7 +2341,7 @@
         <v>266</v>
       </c>
       <c r="D28" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2349,7 +2355,7 @@
         <v>266</v>
       </c>
       <c r="D29" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2363,7 +2369,7 @@
         <v>266</v>
       </c>
       <c r="D30" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2377,7 +2383,7 @@
         <v>264</v>
       </c>
       <c r="D31" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2391,7 +2397,7 @@
         <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2405,7 +2411,7 @@
         <v>266</v>
       </c>
       <c r="D33" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2419,7 +2425,7 @@
         <v>266</v>
       </c>
       <c r="D34" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2433,7 +2439,7 @@
         <v>264</v>
       </c>
       <c r="D35" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2447,7 +2453,7 @@
         <v>264</v>
       </c>
       <c r="D36" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2458,10 +2464,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D37" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2475,7 +2481,7 @@
         <v>267</v>
       </c>
       <c r="D38" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2486,10 +2492,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D39" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2503,7 +2509,7 @@
         <v>266</v>
       </c>
       <c r="D40" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2517,7 +2523,7 @@
         <v>266</v>
       </c>
       <c r="D41" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2531,7 +2537,7 @@
         <v>266</v>
       </c>
       <c r="D42" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2542,10 +2548,10 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D43" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2559,7 +2565,7 @@
         <v>267</v>
       </c>
       <c r="D44" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2573,7 +2579,7 @@
         <v>266</v>
       </c>
       <c r="D45" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2587,7 +2593,7 @@
         <v>265</v>
       </c>
       <c r="D46" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2601,7 +2607,7 @@
         <v>267</v>
       </c>
       <c r="D47" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2615,7 +2621,7 @@
         <v>267</v>
       </c>
       <c r="D48" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2629,7 +2635,7 @@
         <v>267</v>
       </c>
       <c r="D49" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2643,7 +2649,7 @@
         <v>266</v>
       </c>
       <c r="D50" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2657,7 +2663,7 @@
         <v>266</v>
       </c>
       <c r="D51" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2671,7 +2677,7 @@
         <v>266</v>
       </c>
       <c r="D52" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2685,7 +2691,7 @@
         <v>266</v>
       </c>
       <c r="D53" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2699,7 +2705,7 @@
         <v>266</v>
       </c>
       <c r="D54" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2713,7 +2719,7 @@
         <v>266</v>
       </c>
       <c r="D55" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2727,7 +2733,7 @@
         <v>264</v>
       </c>
       <c r="D56" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2741,7 +2747,7 @@
         <v>264</v>
       </c>
       <c r="D57" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2755,7 +2761,7 @@
         <v>264</v>
       </c>
       <c r="D58" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2769,7 +2775,7 @@
         <v>266</v>
       </c>
       <c r="D59" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2783,7 +2789,7 @@
         <v>264</v>
       </c>
       <c r="D60" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2797,7 +2803,7 @@
         <v>264</v>
       </c>
       <c r="D61" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2811,7 +2817,7 @@
         <v>264</v>
       </c>
       <c r="D62" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2822,10 +2828,10 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D63" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2839,7 +2845,7 @@
         <v>266</v>
       </c>
       <c r="D64" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2853,7 +2859,7 @@
         <v>266</v>
       </c>
       <c r="D65" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2864,10 +2870,10 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D66" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2881,7 +2887,7 @@
         <v>266</v>
       </c>
       <c r="D67" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2895,7 +2901,7 @@
         <v>267</v>
       </c>
       <c r="D68" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2909,7 +2915,7 @@
         <v>267</v>
       </c>
       <c r="D69" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2923,7 +2929,7 @@
         <v>264</v>
       </c>
       <c r="D70" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2934,10 +2940,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="D71" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2951,7 +2957,7 @@
         <v>266</v>
       </c>
       <c r="D72" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2962,10 +2968,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D73" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2976,10 +2982,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D74" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2993,7 +2999,7 @@
         <v>267</v>
       </c>
       <c r="D75" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -3004,10 +3010,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D76" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3021,7 +3027,7 @@
         <v>265</v>
       </c>
       <c r="D77" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3035,7 +3041,7 @@
         <v>265</v>
       </c>
       <c r="D78" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3049,7 +3055,7 @@
         <v>265</v>
       </c>
       <c r="D79" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3063,7 +3069,7 @@
         <v>265</v>
       </c>
       <c r="D80" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3077,7 +3083,7 @@
         <v>265</v>
       </c>
       <c r="D81" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3091,7 +3097,7 @@
         <v>265</v>
       </c>
       <c r="D82" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3102,10 +3108,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D83" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3116,10 +3122,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D84" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3130,10 +3136,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D85" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3144,10 +3150,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D86" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3158,10 +3164,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D87" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3172,10 +3178,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D88" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3189,7 +3195,7 @@
         <v>264</v>
       </c>
       <c r="D89" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3203,7 +3209,7 @@
         <v>264</v>
       </c>
       <c r="D90" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3217,7 +3223,7 @@
         <v>264</v>
       </c>
       <c r="D91" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3231,7 +3237,7 @@
         <v>264</v>
       </c>
       <c r="D92" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3245,7 +3251,7 @@
         <v>264</v>
       </c>
       <c r="D93" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3259,7 +3265,7 @@
         <v>264</v>
       </c>
       <c r="D94" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3273,7 +3279,7 @@
         <v>264</v>
       </c>
       <c r="D95" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3287,7 +3293,7 @@
         <v>264</v>
       </c>
       <c r="D96" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3301,7 +3307,7 @@
         <v>264</v>
       </c>
       <c r="D97" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3315,7 +3321,7 @@
         <v>264</v>
       </c>
       <c r="D98" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3329,7 +3335,7 @@
         <v>264</v>
       </c>
       <c r="D99" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3343,7 +3349,7 @@
         <v>264</v>
       </c>
       <c r="D100" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3357,7 +3363,7 @@
         <v>264</v>
       </c>
       <c r="D101" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3371,7 +3377,7 @@
         <v>264</v>
       </c>
       <c r="D102" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3385,7 +3391,7 @@
         <v>264</v>
       </c>
       <c r="D103" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3399,7 +3405,7 @@
         <v>264</v>
       </c>
       <c r="D104" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3413,7 +3419,7 @@
         <v>266</v>
       </c>
       <c r="D105" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3427,7 +3433,7 @@
         <v>266</v>
       </c>
       <c r="D106" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3441,7 +3447,7 @@
         <v>264</v>
       </c>
       <c r="D107" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3455,7 +3461,7 @@
         <v>266</v>
       </c>
       <c r="D108" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3469,7 +3475,7 @@
         <v>267</v>
       </c>
       <c r="D109" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3483,7 +3489,7 @@
         <v>267</v>
       </c>
       <c r="D110" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3497,7 +3503,7 @@
         <v>264</v>
       </c>
       <c r="D111" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3508,10 +3514,10 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D112" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3525,7 +3531,7 @@
         <v>267</v>
       </c>
       <c r="D113" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3539,7 +3545,7 @@
         <v>267</v>
       </c>
       <c r="D114" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3553,7 +3559,7 @@
         <v>264</v>
       </c>
       <c r="D115" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3567,7 +3573,7 @@
         <v>264</v>
       </c>
       <c r="D116" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3581,7 +3587,7 @@
         <v>266</v>
       </c>
       <c r="D117" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3595,7 +3601,7 @@
         <v>264</v>
       </c>
       <c r="D118" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3609,7 +3615,7 @@
         <v>264</v>
       </c>
       <c r="D119" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3620,10 +3626,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D120" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3637,7 +3643,7 @@
         <v>267</v>
       </c>
       <c r="D121" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3651,7 +3657,7 @@
         <v>267</v>
       </c>
       <c r="D122" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3665,7 +3671,7 @@
         <v>267</v>
       </c>
       <c r="D123" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3679,7 +3685,7 @@
         <v>267</v>
       </c>
       <c r="D124" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3693,7 +3699,7 @@
         <v>267</v>
       </c>
       <c r="D125" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3704,10 +3710,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D126" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3721,7 +3727,7 @@
         <v>267</v>
       </c>
       <c r="D127" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3735,7 +3741,7 @@
         <v>264</v>
       </c>
       <c r="D128" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3749,7 +3755,7 @@
         <v>264</v>
       </c>
       <c r="D129" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3763,7 +3769,7 @@
         <v>264</v>
       </c>
       <c r="D130" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3777,7 +3783,7 @@
         <v>264</v>
       </c>
       <c r="D131" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3791,7 +3797,7 @@
         <v>264</v>
       </c>
       <c r="D132" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3805,7 +3811,7 @@
         <v>264</v>
       </c>
       <c r="D133" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3819,7 +3825,7 @@
         <v>264</v>
       </c>
       <c r="D134" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3833,7 +3839,7 @@
         <v>264</v>
       </c>
       <c r="D135" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3844,10 +3850,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D136" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3858,10 +3864,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D137" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3875,7 +3881,7 @@
         <v>266</v>
       </c>
       <c r="D138" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3889,7 +3895,7 @@
         <v>266</v>
       </c>
       <c r="D139" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3903,7 +3909,7 @@
         <v>264</v>
       </c>
       <c r="D140" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3917,7 +3923,7 @@
         <v>264</v>
       </c>
       <c r="D141" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3931,7 +3937,7 @@
         <v>266</v>
       </c>
       <c r="D142" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3945,7 +3951,7 @@
         <v>264</v>
       </c>
       <c r="D143" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3959,7 +3965,7 @@
         <v>265</v>
       </c>
       <c r="D144" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3973,7 +3979,7 @@
         <v>265</v>
       </c>
       <c r="D145" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3987,7 +3993,7 @@
         <v>265</v>
       </c>
       <c r="D146" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -4001,7 +4007,7 @@
         <v>265</v>
       </c>
       <c r="D147" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4012,10 +4018,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D148" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4029,7 +4035,7 @@
         <v>264</v>
       </c>
       <c r="D149" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4043,7 +4049,7 @@
         <v>267</v>
       </c>
       <c r="D150" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4057,7 +4063,7 @@
         <v>264</v>
       </c>
       <c r="D151" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4071,7 +4077,7 @@
         <v>267</v>
       </c>
       <c r="D152" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4085,7 +4091,7 @@
         <v>264</v>
       </c>
       <c r="D153" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4099,7 +4105,7 @@
         <v>266</v>
       </c>
       <c r="D154" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4113,7 +4119,7 @@
         <v>266</v>
       </c>
       <c r="D155" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4127,7 +4133,7 @@
         <v>266</v>
       </c>
       <c r="D156" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4141,7 +4147,7 @@
         <v>264</v>
       </c>
       <c r="D157" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4155,7 +4161,7 @@
         <v>264</v>
       </c>
       <c r="D158" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4169,7 +4175,7 @@
         <v>264</v>
       </c>
       <c r="D159" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4183,7 +4189,7 @@
         <v>264</v>
       </c>
       <c r="D160" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4197,7 +4203,7 @@
         <v>264</v>
       </c>
       <c r="D161" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4211,7 +4217,7 @@
         <v>264</v>
       </c>
       <c r="D162" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4225,7 +4231,7 @@
         <v>264</v>
       </c>
       <c r="D163" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4239,7 +4245,7 @@
         <v>264</v>
       </c>
       <c r="D164" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4253,7 +4259,7 @@
         <v>264</v>
       </c>
       <c r="D165" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4267,7 +4273,7 @@
         <v>264</v>
       </c>
       <c r="D166" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4281,7 +4287,7 @@
         <v>264</v>
       </c>
       <c r="D167" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4295,7 +4301,7 @@
         <v>264</v>
       </c>
       <c r="D168" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4309,7 +4315,7 @@
         <v>264</v>
       </c>
       <c r="D169" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4323,7 +4329,7 @@
         <v>264</v>
       </c>
       <c r="D170" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4337,7 +4343,7 @@
         <v>264</v>
       </c>
       <c r="D171" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4351,7 +4357,7 @@
         <v>264</v>
       </c>
       <c r="D172" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4365,7 +4371,7 @@
         <v>264</v>
       </c>
       <c r="D173" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4379,7 +4385,7 @@
         <v>264</v>
       </c>
       <c r="D174" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4393,7 +4399,7 @@
         <v>264</v>
       </c>
       <c r="D175" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4407,7 +4413,7 @@
         <v>264</v>
       </c>
       <c r="D176" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4421,7 +4427,7 @@
         <v>264</v>
       </c>
       <c r="D177" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4435,7 +4441,7 @@
         <v>264</v>
       </c>
       <c r="D178" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4449,7 +4455,7 @@
         <v>264</v>
       </c>
       <c r="D179" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4463,7 +4469,7 @@
         <v>264</v>
       </c>
       <c r="D180" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4477,7 +4483,7 @@
         <v>266</v>
       </c>
       <c r="D181" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4491,7 +4497,7 @@
         <v>264</v>
       </c>
       <c r="D182" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4505,7 +4511,7 @@
         <v>266</v>
       </c>
       <c r="D183" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4519,7 +4525,7 @@
         <v>266</v>
       </c>
       <c r="D184" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4533,7 +4539,7 @@
         <v>266</v>
       </c>
       <c r="D185" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4544,10 +4550,10 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D186" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4561,7 +4567,7 @@
         <v>266</v>
       </c>
       <c r="D187" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4575,7 +4581,7 @@
         <v>266</v>
       </c>
       <c r="D188" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4589,7 +4595,7 @@
         <v>266</v>
       </c>
       <c r="D189" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4603,7 +4609,7 @@
         <v>266</v>
       </c>
       <c r="D190" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4617,7 +4623,7 @@
         <v>266</v>
       </c>
       <c r="D191" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4631,7 +4637,7 @@
         <v>264</v>
       </c>
       <c r="D192" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4645,7 +4651,7 @@
         <v>266</v>
       </c>
       <c r="D193" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4659,7 +4665,7 @@
         <v>266</v>
       </c>
       <c r="D194" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4673,7 +4679,7 @@
         <v>266</v>
       </c>
       <c r="D195" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4687,7 +4693,7 @@
         <v>266</v>
       </c>
       <c r="D196" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4701,7 +4707,7 @@
         <v>264</v>
       </c>
       <c r="D197" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4715,7 +4721,7 @@
         <v>264</v>
       </c>
       <c r="D198" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4729,7 +4735,7 @@
         <v>267</v>
       </c>
       <c r="D199" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4740,10 +4746,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D200" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4757,7 +4763,7 @@
         <v>264</v>
       </c>
       <c r="D201" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4771,7 +4777,7 @@
         <v>264</v>
       </c>
       <c r="D202" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4785,7 +4791,7 @@
         <v>264</v>
       </c>
       <c r="D203" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4799,7 +4805,7 @@
         <v>264</v>
       </c>
       <c r="D204" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4813,7 +4819,7 @@
         <v>264</v>
       </c>
       <c r="D205" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4827,7 +4833,7 @@
         <v>266</v>
       </c>
       <c r="D206" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4841,7 +4847,7 @@
         <v>264</v>
       </c>
       <c r="D207" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4855,7 +4861,7 @@
         <v>266</v>
       </c>
       <c r="D208" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4869,7 +4875,7 @@
         <v>266</v>
       </c>
       <c r="D209" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4883,7 +4889,7 @@
         <v>266</v>
       </c>
       <c r="D210" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4897,7 +4903,7 @@
         <v>266</v>
       </c>
       <c r="D211" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4911,7 +4917,7 @@
         <v>266</v>
       </c>
       <c r="D212" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4925,7 +4931,7 @@
         <v>264</v>
       </c>
       <c r="D213" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4939,7 +4945,7 @@
         <v>264</v>
       </c>
       <c r="D214" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4953,7 +4959,7 @@
         <v>264</v>
       </c>
       <c r="D215" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4967,7 +4973,7 @@
         <v>264</v>
       </c>
       <c r="D216" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4981,7 +4987,7 @@
         <v>264</v>
       </c>
       <c r="D217" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4995,7 +5001,7 @@
         <v>264</v>
       </c>
       <c r="D218" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5009,7 +5015,7 @@
         <v>264</v>
       </c>
       <c r="D219" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5023,7 +5029,7 @@
         <v>264</v>
       </c>
       <c r="D220" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5037,7 +5043,7 @@
         <v>266</v>
       </c>
       <c r="D221" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5051,7 +5057,7 @@
         <v>266</v>
       </c>
       <c r="D222" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5065,7 +5071,7 @@
         <v>264</v>
       </c>
       <c r="D223" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5079,7 +5085,7 @@
         <v>266</v>
       </c>
       <c r="D224" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5093,7 +5099,7 @@
         <v>266</v>
       </c>
       <c r="D225" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5107,7 +5113,7 @@
         <v>266</v>
       </c>
       <c r="D226" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5121,7 +5127,7 @@
         <v>266</v>
       </c>
       <c r="D227" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5135,7 +5141,7 @@
         <v>266</v>
       </c>
       <c r="D228" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5149,7 +5155,7 @@
         <v>266</v>
       </c>
       <c r="D229" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5163,7 +5169,7 @@
         <v>266</v>
       </c>
       <c r="D230" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5177,7 +5183,7 @@
         <v>266</v>
       </c>
       <c r="D231" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5191,7 +5197,7 @@
         <v>264</v>
       </c>
       <c r="D232" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5205,7 +5211,7 @@
         <v>264</v>
       </c>
       <c r="D233" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5219,7 +5225,7 @@
         <v>264</v>
       </c>
       <c r="D234" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5233,7 +5239,7 @@
         <v>264</v>
       </c>
       <c r="D235" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5247,7 +5253,7 @@
         <v>264</v>
       </c>
       <c r="D236" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5261,7 +5267,7 @@
         <v>264</v>
       </c>
       <c r="D237" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5275,7 +5281,7 @@
         <v>264</v>
       </c>
       <c r="D238" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5289,7 +5295,7 @@
         <v>264</v>
       </c>
       <c r="D239" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5303,7 +5309,7 @@
         <v>264</v>
       </c>
       <c r="D240" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5317,7 +5323,7 @@
         <v>264</v>
       </c>
       <c r="D241" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5331,7 +5337,7 @@
         <v>264</v>
       </c>
       <c r="D242" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5345,7 +5351,7 @@
         <v>266</v>
       </c>
       <c r="D243" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5359,7 +5365,7 @@
         <v>266</v>
       </c>
       <c r="D244" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5373,7 +5379,7 @@
         <v>266</v>
       </c>
       <c r="D245" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5387,7 +5393,7 @@
         <v>266</v>
       </c>
       <c r="D246" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5401,7 +5407,7 @@
         <v>266</v>
       </c>
       <c r="D247" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5415,7 +5421,7 @@
         <v>264</v>
       </c>
       <c r="D248" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5429,7 +5435,7 @@
         <v>266</v>
       </c>
       <c r="D249" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5443,7 +5449,7 @@
         <v>266</v>
       </c>
       <c r="D250" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5457,7 +5463,7 @@
         <v>264</v>
       </c>
       <c r="D251" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5471,7 +5477,7 @@
         <v>265</v>
       </c>
       <c r="D252" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5485,7 +5491,7 @@
         <v>265</v>
       </c>
       <c r="D253" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5499,7 +5505,7 @@
         <v>265</v>
       </c>
       <c r="D254" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5513,7 +5519,7 @@
         <v>265</v>
       </c>
       <c r="D255" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5527,7 +5533,7 @@
         <v>264</v>
       </c>
       <c r="D256" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
   </sheetData>
